--- a/ZumNet.Web/Content/Forms/IMPORT/FORM_PURCHASEUCC.xlsx
+++ b/ZumNet.Web/Content/Forms/IMPORT/FORM_PURCHASEUCC.xlsx
@@ -1,46 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\새 폴더 (3)\새 폴더\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\byrlee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FACC2D9-36E0-48BC-A0A7-F735B39402AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18810" windowHeight="12420"/>
+    <workbookView xWindow="-24885" yWindow="1455" windowWidth="24870" windowHeight="16005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="145621"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>품번</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>TTL L/T</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>L/T</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>업체코드</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>BPA</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>적용시점</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -49,10 +43,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>모델번호</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>개발견적가</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -61,62 +51,63 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>EMB-SSG200STWA</t>
-  </si>
-  <si>
-    <t>CKN-0401UZZ-WA</t>
-  </si>
-  <si>
-    <t>CLH-0610LZX-WA</t>
-  </si>
-  <si>
-    <t>19951-B-00001</t>
-  </si>
-  <si>
-    <t>현행가</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>확정가</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Pre L/T</t>
+    <t>사업장</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Post L/T</t>
+    <t>모델명</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>NO</t>
+    <t>UOM</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>법인명</t>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>LT</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>CT</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>KH</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>CD</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>OTB-CHE001BAGA</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>VH</t>
+  </si>
+  <si>
+    <t>OTB-SON037/BK</t>
+  </si>
+  <si>
+    <t>OTB-SEK340PPBA</t>
+  </si>
+  <si>
+    <t>CZL-0151CEZ-ZA</t>
+  </si>
+  <si>
+    <t>CZL-0151CNZ-ZA</t>
+  </si>
+  <si>
+    <t>CUS-5784ZZO-WA</t>
+  </si>
+  <si>
+    <t>221107</t>
+  </si>
+  <si>
+    <t>220135</t>
+  </si>
+  <si>
+    <t>인쇄상이</t>
+  </si>
+  <si>
+    <t>CD 이관품</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
     <numFmt numFmtId="177" formatCode="#,##0.00000_);[Red]\(#,##0.00000\)"/>
@@ -725,7 +716,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -751,9 +742,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -815,9 +803,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -855,9 +843,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -892,7 +880,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -927,7 +915,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1100,241 +1088,154 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9" style="8"/>
-    <col min="3" max="3" width="16.58203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.08203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" style="6" customWidth="1"/>
-    <col min="9" max="9" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="9" style="7"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="8"/>
+    <col min="2" max="2" width="16.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="7"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>19</v>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="5">
+        <v>231</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="5">
+        <v>231</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4">
+        <v>46023</v>
+      </c>
+      <c r="J2" s="3">
+        <v>23</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="5">
+        <v>231</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5">
+        <v>231</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="4">
+        <v>46023</v>
+      </c>
+      <c r="J3" s="3">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A2" s="8">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="D4" s="5">
+        <v>265</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5">
+        <v>265</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="4">
+        <v>46023</v>
+      </c>
+      <c r="J4" s="3">
+        <v>23</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5">
-        <v>677</v>
-      </c>
-      <c r="H2" s="5">
-        <v>677</v>
-      </c>
-      <c r="I2" s="1">
-        <v>19951</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="4">
-        <v>42461</v>
-      </c>
-      <c r="L2" s="3">
-        <v>7</v>
-      </c>
-      <c r="M2" s="3">
-        <v>3</v>
-      </c>
-      <c r="N2" s="3">
-        <v>3</v>
-      </c>
-      <c r="O2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="9">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5">
-        <v>805</v>
-      </c>
-      <c r="H3" s="5">
-        <v>805</v>
-      </c>
-      <c r="I3" s="2">
-        <v>19951</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="4">
-        <v>42461</v>
-      </c>
-      <c r="L3" s="3">
-        <v>7</v>
-      </c>
-      <c r="M3" s="3">
-        <v>3</v>
-      </c>
-      <c r="N3" s="3">
-        <v>3</v>
-      </c>
-      <c r="O3" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A4" s="8">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="5">
-        <v>886</v>
-      </c>
-      <c r="H4" s="5">
-        <v>886</v>
-      </c>
-      <c r="I4" s="1">
-        <v>19951</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="4">
-        <v>42461</v>
-      </c>
-      <c r="L4" s="3">
-        <v>7</v>
-      </c>
-      <c r="M4" s="3">
-        <v>3</v>
-      </c>
-      <c r="N4" s="3">
-        <v>3</v>
-      </c>
-      <c r="O4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2261</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2261</v>
-      </c>
-      <c r="I5" s="1">
-        <v>19951</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="4">
-        <v>42461</v>
-      </c>
-      <c r="L5" s="3">
-        <v>7</v>
-      </c>
-      <c r="M5" s="3">
-        <v>3</v>
-      </c>
-      <c r="N5" s="3">
-        <v>3</v>
-      </c>
-      <c r="O5" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
